--- a/outputs/35747.xlsx
+++ b/outputs/35747.xlsx
@@ -235,71 +235,71 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -553,7 +553,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:V11"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="9.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="3" style="1" width="9.5"/>
@@ -595,7 +595,7 @@
         <v>44933</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -634,7 +634,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
         <v>2</v>
       </c>
@@ -666,7 +666,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
         <v>3</v>
       </c>
@@ -698,7 +698,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
         <v>4</v>
       </c>
@@ -730,7 +730,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
         <v>1</v>
       </c>
@@ -762,7 +762,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
         <v>5</v>
       </c>
@@ -801,7 +801,7 @@
       <c r="U7" s="5"/>
       <c r="V7" s="5"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
         <v>6</v>
       </c>
@@ -833,7 +833,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -865,7 +865,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
         <v>8</v>
       </c>

--- a/outputs/35747.xlsx
+++ b/outputs/35747.xlsx
@@ -595,7 +595,7 @@
         <v>44933</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -634,7 +634,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
         <v>2</v>
       </c>
@@ -666,7 +666,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
         <v>3</v>
       </c>
@@ -698,7 +698,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
         <v>4</v>
       </c>
@@ -730,7 +730,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
         <v>1</v>
       </c>
@@ -762,7 +762,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
         <v>5</v>
       </c>
@@ -801,7 +801,7 @@
       <c r="U7" s="5"/>
       <c r="V7" s="5"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
         <v>6</v>
       </c>
@@ -833,7 +833,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -865,7 +865,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
         <v>8</v>
       </c>
